--- a/assets/constructions/examples/ctd_mih_90.xlsx
+++ b/assets/constructions/examples/ctd_mih_90.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,58 +594,78 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AJU-20-M10-2T</t>
+          <t>MT190-032G16R04BD12-IK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AJU</t>
+          <t>MT190-G...BD12-IK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>63</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CCMT060204/CPMT090204Z</t>
-        </is>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
+          <t>BDMT1204...R</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>90</v>
       </c>
@@ -654,76 +674,84 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M16</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ISO_CC0602H+ISO_CP0902H</t>
+          <t>SKIF_BD1204H</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>22</v>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>CC0602H</t>
+          <t>SKIF_BD1204H</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2019/ Основной каталог СКИФ-М</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT190-040G20R04LN16-IK</t>
+          <t>017R20090-04-04-M08025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MT190-G...LN16-IK</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>67</v>
-      </c>
+        <v>8.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -731,20 +759,20 @@
       <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>LNMU160708SR</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
       <c r="S3" t="n">
         <v>90</v>
       </c>
@@ -753,19 +781,19 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M20</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SKIF_LN1607H</t>
+          <t>PALB_XP0602H</t>
         </is>
       </c>
       <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
         <v>2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
@@ -776,73 +804,85 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>M20</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>30</v>
-      </c>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>SKIF_LN1607H</t>
+          <t>PALB_XP0602_H</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
+          <t>2020 / PALBIT основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>209.57</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>19266.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>020R20090-05-04-M10030</t>
+          <t>300R-26-M12-3T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>300R/400R</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>18</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>APMT1135</t>
+        </is>
+      </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
@@ -854,60 +894,74 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>PALB_XP0602H</t>
+          <t>DER_AP1135H</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>PALB_XP0602_H</t>
+          <t>AP1135_H</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2020 / PALBIT основной каталог EN</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>4955.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT190-016G08R04BD08-IK</t>
+          <t>VSM11D016Z02M08XD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT190-G...BD08</t>
+          <t>VSM11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -915,36 +969,38 @@
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>44</v>
-      </c>
+        <v>8.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>41400</v>
+      </c>
       <c r="O5" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>BDMT0803..R</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
       <c r="S5" t="n">
         <v>90</v>
       </c>
@@ -958,7 +1014,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SKIF_BD0803H</t>
+          <t>WIDIA_XD1104H</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -976,7 +1032,7 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>M08</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="AC5" t="n">
@@ -985,67 +1041,77 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>SKIF_BD0803H</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>WID_XD1104_H</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>WID_VSM11D_1631</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2018 / WIDIA достижения</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT190-016G08R01LN11-IK</t>
+          <t>025R17090-04-09-M12035</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MT190-G...LN11-IK</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>45</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>LNMU110408SR</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
       <c r="S6" t="n">
         <v>90</v>
       </c>
@@ -1054,19 +1120,19 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M8</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SKIF_LN1104H</t>
+          <t>PALB_AP1003H</t>
         </is>
       </c>
       <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
         <v>2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
@@ -1077,23 +1143,35 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>M08</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>10</v>
-      </c>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>SKIF_LN1104H</t>
+          <t>PALB_AP1003_H</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
+          <t>2020 / PALBIT основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>244.19</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>22449.29</v>
       </c>
     </row>
   </sheetData>
